--- a/examples/wangetal2018/out/ResultFiles/AC_0.5_nfc.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_0.5_nfc.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="351">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>nfc</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,27 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
+    <t>b</t>
   </si>
   <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,28 +133,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>nfc</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -144,6 +178,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -180,6 +217,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -192,6 +235,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -201,27 +247,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -234,39 +301,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -282,6 +340,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -339,15 +400,6 @@
     <t>C_0_1</t>
   </si>
   <si>
-    <t>C_0_2</t>
-  </si>
-  <si>
-    <t>C_0_3</t>
-  </si>
-  <si>
-    <t>C_0_4</t>
-  </si>
-  <si>
     <t>CS1</t>
   </si>
   <si>
@@ -363,21 +415,6 @@
     <t>C_1_3</t>
   </si>
   <si>
-    <t>C_1_4</t>
-  </si>
-  <si>
-    <t>C_1_5</t>
-  </si>
-  <si>
-    <t>C_1_6</t>
-  </si>
-  <si>
-    <t>C_1_7</t>
-  </si>
-  <si>
-    <t>C_1_8</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
@@ -387,9 +424,6 @@
     <t>C_2_1</t>
   </si>
   <si>
-    <t>C_2_2</t>
-  </si>
-  <si>
     <t>CS3</t>
   </si>
   <si>
@@ -399,9 +433,6 @@
     <t>C_3_1</t>
   </si>
   <si>
-    <t>C_3_2</t>
-  </si>
-  <si>
     <t>Pipe segment</t>
   </si>
   <si>
@@ -450,339 +481,237 @@
     <t>Erosional velocity (m/s)</t>
   </si>
   <si>
-    <t>PI01_0_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>PI01_0_remaining</t>
-  </si>
-  <si>
-    <t>PI01_1_pre_C_0_1</t>
+    <t>PI01_0</t>
+  </si>
+  <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>PI01_1_pre_C_0_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_0</t>
   </si>
   <si>
     <t>PI01_1_remaining</t>
   </si>
   <si>
-    <t>PI01_pre_C_0_2</t>
-  </si>
-  <si>
-    <t>PI01_remaining</t>
-  </si>
-  <si>
-    <t>PI02_0_pre_C_0_3</t>
+    <t>N_post_C_0_0</t>
+  </si>
+  <si>
+    <t>N01_1</t>
+  </si>
+  <si>
+    <t>PI01</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
+    <t>PI02_0_pre_C_0_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_1</t>
   </si>
   <si>
     <t>PI02_0_remaining</t>
   </si>
   <si>
-    <t>PI02_pre_C_0_4</t>
-  </si>
-  <si>
-    <t>PI02_remaining</t>
-  </si>
-  <si>
-    <t>PI03_0_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI03_0_remaining</t>
-  </si>
-  <si>
-    <t>PI03_pre_C_1_1</t>
+    <t>N_post_C_0_1</t>
+  </si>
+  <si>
+    <t>N02_0</t>
+  </si>
+  <si>
+    <t>PI02</t>
+  </si>
+  <si>
+    <t>N03</t>
+  </si>
+  <si>
+    <t>PI03_0</t>
+  </si>
+  <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
+    <t>PI03_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_0</t>
   </si>
   <si>
     <t>PI03_remaining</t>
   </si>
   <si>
-    <t>PI04_0_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>PI04_0_remaining</t>
-  </si>
-  <si>
-    <t>PI04_1_pre_C_1_3</t>
+    <t>N_post_C_1_0</t>
+  </si>
+  <si>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0</t>
+  </si>
+  <si>
+    <t>N04_0</t>
+  </si>
+  <si>
+    <t>PI04_1_pre_C_1_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_1</t>
   </si>
   <si>
     <t>PI04_1_remaining</t>
   </si>
   <si>
-    <t>PI04_pre_C_1_4</t>
-  </si>
-  <si>
-    <t>PI04_pre_C_1_5</t>
+    <t>N_post_C_1_1</t>
+  </si>
+  <si>
+    <t>N04_1</t>
+  </si>
+  <si>
+    <t>PI04_pre_C_1_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_2</t>
   </si>
   <si>
     <t>PI04_remaining</t>
   </si>
   <si>
-    <t>PI05_0_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>PI05_0_remaining</t>
-  </si>
-  <si>
-    <t>PI05_1_pre_C_1_7</t>
+    <t>N_post_C_1_2</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>PI05_0</t>
+  </si>
+  <si>
+    <t>N05_0</t>
+  </si>
+  <si>
+    <t>PI05_1_pre_C_1_3</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_3</t>
   </si>
   <si>
     <t>PI05_1_remaining</t>
   </si>
   <si>
-    <t>PI05_pre_C_1_8</t>
-  </si>
-  <si>
-    <t>PI05_remaining</t>
+    <t>N_post_C_1_3</t>
+  </si>
+  <si>
+    <t>N05_1</t>
+  </si>
+  <si>
+    <t>PI05</t>
+  </si>
+  <si>
+    <t>N06</t>
   </si>
   <si>
     <t>PI06_0</t>
   </si>
   <si>
-    <t>PI06_1_pre_C_2_0</t>
-  </si>
-  <si>
-    <t>PI06_1_remaining</t>
-  </si>
-  <si>
-    <t>PI06</t>
-  </si>
-  <si>
-    <t>PI07_0_remaining</t>
-  </si>
-  <si>
-    <t>PI07_1_pre_C_2_2</t>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
+    <t>PI06_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_2_0</t>
+  </si>
+  <si>
+    <t>PI06_remaining</t>
+  </si>
+  <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>PI07_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_2_1</t>
   </si>
   <si>
     <t>PI07_1_remaining</t>
   </si>
   <si>
+    <t>N07_0</t>
+  </si>
+  <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
-    <t>PI08_1_pre_C_3_0</t>
-  </si>
-  <si>
-    <t>PI08_1_remaining</t>
-  </si>
-  <si>
-    <t>PI08</t>
-  </si>
-  <si>
-    <t>PI09_0_remaining</t>
-  </si>
-  <si>
-    <t>PI09_1_pre_C_3_2</t>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
+    <t>PI08_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_3_0</t>
+  </si>
+  <si>
+    <t>PI08_remaining</t>
+  </si>
+  <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
+    <t>N09</t>
+  </si>
+  <si>
+    <t>PI09_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_3_1</t>
   </si>
   <si>
     <t>PI09_1_remaining</t>
   </si>
   <si>
+    <t>N09_0</t>
+  </si>
+  <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_1</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N_post_C_0_2</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N_post_C_0_3</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_4</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N_post_C_1_2</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_3</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_4</t>
-  </si>
-  <si>
-    <t>N_post_C_1_5</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N_post_C_1_6</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_7</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_8</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_1</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_2</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_3_1</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_2</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_3</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_4</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_3</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_4</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_5</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_7</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_8</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_0</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_2</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_0</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_2</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -850,22 +779,316 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>159148723.5183168</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(27.046985282253413), '2049': np.float64(27.723159914309747), '2050': np.float64(28.416238912167486), '2051': np.float64(29.126644884971675), '2052': np.float64(29.85481100709596), '2053': np.float64(30.60118128227336), '2054': np.float64(31.366210814330188), '2055': np.float64(32.150366084688436), '2056': np.float64(32.954125236805645), '2057': np.float64(33.77797836772578), '2058': np.float64(34.62242782691893), '2059': np.float64(35.48798852259189), '2060': np.float64(36.37518823565669), '2061': np.float64(37.284567941548104), '2062': np.float64(38.2166821400868), '2063': np.float64(39.17209919358897), '2064': np.float64(40.151401673428694), '2065': np.float64(41.155186715264406), '2066': np.float64(42.18406638314601), '2067': np.float64(43.238668042724655), '2068': np.float64(44.319634743792776), '2069': np.float64(45.42762561238759), '2070': np.float64(46.56331625269728), '2071': np.float64(47.7273991590147), '2072': np.float64(48.92058413799006), '2073': np.float64(50.14359874143982), '2074': np.float64(51.3971887099758), '2075': np.float64(52.68211842772519), '2076': np.float64(53.99917138841832), '2077': np.float64(55.34915067312877), '2078': np.float64(56.732879439956996), '2079': np.float64(58.1512014259559), '2080': np.float64(59.604981461604794), '2081': np.float64(61.095105998144916), '2082': np.float64(62.62248364809852), '2020': np.float64(13.54723404173073), '2021': np.float64(13.885914892773997), '2022': np.float64(14.233062765093345), '2023': np.float64(14.588889334220678), '2024': np.float64(14.953611567576193), '2025': np.float64(15.327451856765595), '2026': np.float64(15.710638153184735), '2027': np.float64(16.103404107014356), '2028': np.float64(16.50598920968971), '2029': np.float64(16.918638939931952), '2030': np.float64(17.341604913430245), '2031': np.float64(17.775145036266004), '2032': np.float64(18.219523662172655), '2033': np.float64(18.675011753726963), '2034': np.float64(19.14188704757014), '2035': np.float64(19.62043422375939), '2036': np.float64(20.110945079353375), '2037': np.float64(20.613718706337206), '2038': np.float64(21.129061673995636), '2039': np.float64(21.65728821584552), '2040': np.float64(22.19872042124166), '2041': np.float64(22.7536884317727), '2042': np.float64(23.322530642567017), '2043': np.float64(23.90559390863119), '2044': np.float64(24.503233756346965), '2045': np.float64(25.11581460025564), '2046': np.float64(25.743709965262028), '2047': np.float64(26.387302714393577)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.03511090585402888</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.3333333354</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -881,7 +1104,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -889,32 +1112,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1228,14 +1433,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1244,28 +1449,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1273,7 +1478,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1281,7 +1486,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1289,15 +1494,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>0.5</v>
@@ -1305,7 +1510,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1313,7 +1518,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1321,7 +1526,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1329,7 +1534,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1337,63 +1542,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>29</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1401,39 +1606,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1443,268 +1709,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
+      <c r="C1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B2">
-        <v>0.7480231655657853</v>
+        <v>0.7064499137683713</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B4">
-        <v>0.1486150257458985</v>
+        <v>0.103073235859883</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>0.03225829042830805</v>
+        <v>0.03286717230059372</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B7">
-        <v>0.006665964150651951</v>
+        <v>0.006791785596201225</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>0.01580374142085102</v>
+        <v>0.01610204029341005</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B10">
-        <v>0.01701801172198347</v>
+        <v>0.01701801172198348</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B11">
-        <v>0.4595510387684817</v>
+        <v>0.4756556590217031</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B15">
-        <v>0.008504988411985933</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B16">
-        <v>0.05621100016341336</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B17">
-        <v>0.003395104754211249</v>
+        <v>0.007185211429761688</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.04438150890927674</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.003375288635558638</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B20">
-        <v>13.54723404173073</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>13.54723404173073</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
@@ -1712,472 +1978,307 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>91139.43584259163</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B27">
-        <v>17897.89890319461</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B28">
-        <v>745.7457876331086</v>
+        <v>83908.29201006162</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>18525.11729865059</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>771.8798874437747</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B31">
-        <v>233798092.8378574</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33">
+        <v>159148723.5183168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39">
         <v>24.24086700823207</v>
       </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40">
+        <v>49.90105577503258</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41">
+        <v>9.609958914811417</v>
+      </c>
+      <c r="C41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52">
-        <v>3.712822449268846</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>4978.969160918507</v>
-      </c>
-      <c r="E52">
-        <v>12106254.18251517</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>35.48634805525908</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53">
-        <v>3.694274907726207</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>4954.096536758998</v>
-      </c>
-      <c r="E53">
-        <v>12078987.97075614</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>35.30907469415853</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54">
-        <v>3.675866416662363</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>4929.410382072562</v>
-      </c>
-      <c r="E54">
-        <v>12051931.50382208</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>35.13313034723929</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55">
-        <v>3.65759532173972</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>4904.9084783594</v>
-      </c>
-      <c r="E55">
-        <v>12025082.23056671</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>34.95849920270307</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56">
-        <v>3.639449428058218</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>4880.574472014631</v>
-      </c>
-      <c r="E56">
-        <v>11998422.11784048</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>34.785064704352</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57">
-        <v>3.621383319123625</v>
-      </c>
-      <c r="C57">
-        <v>12.5</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G57">
-        <v>34.61239277122915</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" t="s">
         <v>108</v>
       </c>
-      <c r="B58">
-        <v>4.071502188759833</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>5459.965865170711</v>
-      </c>
-      <c r="E58">
-        <v>12634599.23977768</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>38.91453085954409</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" t="s">
+        <v>109</v>
+      </c>
+      <c r="F54" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H54" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59">
-        <v>4.04901747742736</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>5429.813417579639</v>
-      </c>
-      <c r="E59">
-        <v>12601419.4133833</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>38.69962688738584</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60">
-        <v>2.651211887480207</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>3555.328165348707</v>
-      </c>
-      <c r="E60">
-        <v>10554287.48727263</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>25.33970559941271</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H60" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B61">
-        <v>2.165949623175708</v>
+        <v>8.085584439241739</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2904.581763671088</v>
+        <v>10842.93044471196</v>
       </c>
       <c r="E61">
-        <v>9953691.026075777</v>
+        <v>18684989.6627345</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>20.70167460157071</v>
+        <v>77.28025445914412</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2185,25 +2286,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B62">
-        <v>2.158284482254466</v>
+        <v>7.988547583644502</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2894.302656392884</v>
+        <v>10712.80208061895</v>
       </c>
       <c r="E62">
-        <v>9953691.026075777</v>
+        <v>18535748.53236309</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>20.62841285465433</v>
+        <v>76.35279733482363</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -2211,25 +2312,25 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B63">
-        <v>2.15066641462957</v>
+        <v>7.893558659679624</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D63">
-        <v>2884.086675346545</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>9953691.026075777</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="G63">
-        <v>20.55560102404852</v>
+        <v>75.44491389486112</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -2237,25 +2338,25 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B64">
-        <v>2.143110269997627</v>
+        <v>8.996183146418002</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>2873.953734272217</v>
+        <v>12064.06152300947</v>
       </c>
       <c r="E64">
-        <v>9953691.026075777</v>
+        <v>20092665.5797895</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64">
-        <v>20.48338103991817</v>
+        <v>85.98355850964867</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -2263,25 +2364,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B65">
-        <v>2.135598101815749</v>
+        <v>5.089319451532429</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2863.879766496955</v>
+        <v>6824.879170894018</v>
       </c>
       <c r="E65">
-        <v>9953691.026075777</v>
+        <v>14144849.90860312</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65">
-        <v>20.41158137311636</v>
+        <v>48.64260650466742</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2289,25 +2390,25 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B66">
-        <v>2.128122766857393</v>
+        <v>4.510063446094772</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2853.855192811102</v>
+        <v>6048.085282482011</v>
       </c>
       <c r="E66">
-        <v>9953691.026075777</v>
+        <v>13283351.63135838</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>20.34013375024011</v>
+        <v>43.10620380754742</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2315,25 +2416,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B67">
-        <v>2.120673415427367</v>
+        <v>4.474932497277989</v>
       </c>
       <c r="C67">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>6000.973977499729</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>13231272.26718051</v>
       </c>
       <c r="F67">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>20.26893447226658</v>
+        <v>42.77042985275748</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -2341,25 +2442,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B68">
-        <v>4.42365841703011</v>
+        <v>4.440341519768192</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D68">
-        <v>5932.214410405718</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>13155296.46749666</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="G68">
-        <v>42.28036336486285</v>
+        <v>42.43981682607586</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -2367,25 +2468,25 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B69">
-        <v>4.38870070420128</v>
+        <v>5.983329646263154</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>5885.335418348</v>
+        <v>8023.764722231816</v>
       </c>
       <c r="E69">
-        <v>13103521.20300996</v>
+        <v>15484786.78923609</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69">
-        <v>41.94624516190274</v>
+        <v>57.18736116736668</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -2393,25 +2494,25 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B70">
-        <v>4.354195018393445</v>
+        <v>5.918477701239929</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>5839.062603565977</v>
+        <v>7936.796966916769</v>
       </c>
       <c r="E70">
-        <v>13052434.20924805</v>
+        <v>15387165.75339465</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>41.6164473347259</v>
+        <v>56.56752040616683</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2419,10 +2520,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B71">
-        <v>4.320154705662414</v>
+        <v>5.854909488873656</v>
       </c>
       <c r="C71">
         <v>12.5</v>
@@ -2437,7 +2538,7 @@
         <v>16916025.69007904</v>
       </c>
       <c r="G71">
-        <v>41.29109744202606</v>
+        <v>55.95994928201454</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -2445,25 +2546,25 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B72">
-        <v>4.286550559506197</v>
+        <v>5.792587314833412</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>5748.350031309</v>
+        <v>7767.975440937902</v>
       </c>
       <c r="E72">
-        <v>12952338.13256341</v>
+        <v>15197852.27000845</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72">
-        <v>40.9699163344204</v>
+        <v>55.36428752070728</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -2471,53 +2572,27 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B73">
-        <v>4.253393562125825</v>
+        <v>5.731474848070139</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>5703.885834681973</v>
+        <v>7686.022400759018</v>
       </c>
       <c r="E73">
-        <v>12903300.65253028</v>
+        <v>15106041.12364851</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
-        <v>40.65300897739369</v>
+        <v>54.78018787799369</v>
       </c>
       <c r="H73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" t="s">
-        <v>124</v>
-      </c>
-      <c r="B74">
-        <v>4.222801507111746</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <v>5662.861277066993</v>
-      </c>
-      <c r="E74">
-        <v>12858071.87062018</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>40.36061678067849</v>
-      </c>
-      <c r="H74">
         <v>0</v>
       </c>
     </row>
@@ -2528,63 +2603,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="A1" t="s">
         <v>135</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="B1" t="s">
         <v>136</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="C1" t="s">
         <v>137</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="D1" t="s">
         <v>138</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="E1" t="s">
         <v>139</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="F1" t="s">
         <v>140</v>
+      </c>
+      <c r="G1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K1" t="s">
+        <v>144</v>
+      </c>
+      <c r="L1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" t="s">
+        <v>146</v>
+      </c>
+      <c r="O1" t="s">
+        <v>147</v>
+      </c>
+      <c r="P1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2592,55 +2667,55 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F2">
-        <v>102.2403209889567</v>
+        <v>102.3585890663991</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K2">
         <v>4.865822962046021</v>
       </c>
       <c r="L2">
-        <v>11.66666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="M2">
-        <v>7.249328333333335</v>
+        <v>8.284946666666665</v>
       </c>
       <c r="N2">
         <v>4865822.962046022</v>
       </c>
       <c r="O2">
-        <v>4380632.115152928</v>
+        <v>4318363.853382817</v>
       </c>
       <c r="P2">
-        <v>17.33857968470129</v>
+        <v>18.93114870746355</v>
       </c>
       <c r="Q2">
-        <v>0.02851201821821069</v>
+        <v>0.03150147624109283</v>
       </c>
       <c r="R2">
-        <v>29.95166196029462</v>
+        <v>29.8189419558771</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2648,55 +2723,55 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F3">
-        <v>102.0813724237844</v>
+        <v>102.3585911705492</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K3">
         <v>4.865822962046021</v>
       </c>
       <c r="L3">
-        <v>1.666666666666668</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="M3">
-        <v>1.035618333333334</v>
+        <v>6.213709999999999</v>
       </c>
       <c r="N3">
-        <v>4865822.962046022</v>
+        <v>4318363.853382817</v>
       </c>
       <c r="O3">
-        <v>4799715.335512225</v>
+        <v>3858388.135997178</v>
       </c>
       <c r="P3">
-        <v>17.17247251116143</v>
+        <v>21.13193656880255</v>
       </c>
       <c r="Q3">
-        <v>0.02819506793993419</v>
+        <v>0.03527149645556138</v>
       </c>
       <c r="R3">
-        <v>28.61421737129472</v>
+        <v>31.50455799459733</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2704,55 +2779,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F4">
-        <v>102.0813727360724</v>
+        <v>102.0110293738117</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>4.865822962046021</v>
       </c>
       <c r="L4">
-        <v>9.999999999999998</v>
+        <v>3.333333333333336</v>
       </c>
       <c r="M4">
-        <v>6.213709999999999</v>
+        <v>2.071236666666668</v>
       </c>
       <c r="N4">
-        <v>4799715.335512225</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O4">
-        <v>4382192.886298967</v>
+        <v>4735652.057229326</v>
       </c>
       <c r="P4">
-        <v>17.20780520968025</v>
+        <v>17.23937054644133</v>
       </c>
       <c r="Q4">
-        <v>0.02829680625249262</v>
+        <v>0.02861288247914779</v>
       </c>
       <c r="R4">
-        <v>29.94632548603582</v>
+        <v>28.50381751054698</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2760,55 +2835,55 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F5">
-        <v>101.9226371489505</v>
+        <v>102.0110294366525</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K5">
         <v>4.865822962046021</v>
       </c>
       <c r="L5">
-        <v>3.333333333333336</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="M5">
-        <v>2.071236666666668</v>
+        <v>8.284946666666665</v>
       </c>
       <c r="N5">
-        <v>4865822.962046022</v>
+        <v>4735652.057229326</v>
       </c>
       <c r="O5">
-        <v>4733096.700577617</v>
+        <v>4175545.321476262</v>
       </c>
       <c r="P5">
-        <v>17.1692805823145</v>
+        <v>19.49711294566231</v>
       </c>
       <c r="Q5">
-        <v>0.02819681361661327</v>
+        <v>0.03247315930594146</v>
       </c>
       <c r="R5">
-        <v>28.8147976413043</v>
+        <v>30.31289954067237</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2816,55 +2891,55 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F6">
-        <v>101.9226371862942</v>
+        <v>102.0110295340685</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K6">
         <v>4.865822962046021</v>
       </c>
       <c r="L6">
-        <v>8.333333333333332</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="M6">
-        <v>5.178091666666666</v>
+        <v>4.142473333333332</v>
       </c>
       <c r="N6">
-        <v>4733096.700577617</v>
+        <v>4175545.321476262</v>
       </c>
       <c r="O6">
-        <v>4383744.658058213</v>
+        <v>3865932.268884428</v>
       </c>
       <c r="P6">
-        <v>17.1987847201437</v>
+        <v>21.02009785691392</v>
       </c>
       <c r="Q6">
-        <v>0.02828181087572244</v>
+        <v>0.03508297460307694</v>
       </c>
       <c r="R6">
-        <v>29.94102260858688</v>
+        <v>31.47456184224362</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2872,55 +2947,55 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F7">
-        <v>101.7646139326433</v>
+        <v>101.6675887116611</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K7">
         <v>4.865822962046021</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="M7">
-        <v>3.106855</v>
+        <v>5.178091666666668</v>
       </c>
       <c r="N7">
         <v>4865822.962046022</v>
       </c>
       <c r="O7">
-        <v>4665941.396452308</v>
+        <v>4535819.686219067</v>
       </c>
       <c r="P7">
-        <v>17.16621746919908</v>
+        <v>17.92139951605183</v>
       </c>
       <c r="Q7">
-        <v>0.0281988499548217</v>
+        <v>0.02978081368764491</v>
       </c>
       <c r="R7">
-        <v>29.0213241053115</v>
+        <v>29.11123235545484</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2928,223 +3003,223 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F8">
-        <v>101.7646139364395</v>
+        <v>101.667588716107</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K8">
         <v>4.865822962046021</v>
       </c>
       <c r="L8">
-        <v>6.666666666666664</v>
+        <v>15</v>
       </c>
       <c r="M8">
-        <v>4.142473333333332</v>
+        <v>9.320565</v>
       </c>
       <c r="N8">
-        <v>4665941.396452308</v>
+        <v>4535819.686219067</v>
       </c>
       <c r="O8">
-        <v>4385287.844681869</v>
+        <v>3873357.822582715</v>
       </c>
       <c r="P8">
-        <v>17.18986940259777</v>
+        <v>20.91015595593554</v>
       </c>
       <c r="Q8">
-        <v>0.02826698951929117</v>
+        <v>0.03489767034654204</v>
       </c>
       <c r="R8">
-        <v>29.93575186193653</v>
+        <v>31.44512068490176</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F9">
-        <v>101.6073676239537</v>
+        <v>101.3282293811371</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K9">
         <v>4.865822962046021</v>
       </c>
       <c r="L9">
-        <v>8.333333333333336</v>
+        <v>15.75</v>
       </c>
       <c r="M9">
-        <v>5.178091666666668</v>
+        <v>9.786593249999999</v>
       </c>
       <c r="N9">
         <v>4865822.962046022</v>
       </c>
       <c r="O9">
-        <v>4528854.089399976</v>
+        <v>4225517.642759564</v>
       </c>
       <c r="P9">
-        <v>17.18702115034849</v>
+        <v>19.14281070666751</v>
       </c>
       <c r="Q9">
-        <v>0.02824738149948417</v>
+        <v>0.03187269332203519</v>
       </c>
       <c r="R9">
-        <v>29.45725358836297</v>
+        <v>30.13724280594112</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F10">
-        <v>101.6073676242719</v>
+        <v>101.3282293813686</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K10">
         <v>4.865822962046021</v>
       </c>
       <c r="L10">
-        <v>3.333333333333329</v>
+        <v>10.25</v>
       </c>
       <c r="M10">
-        <v>2.071236666666664</v>
+        <v>6.36905275</v>
       </c>
       <c r="N10">
-        <v>4528854.089399976</v>
+        <v>4225517.642759564</v>
       </c>
       <c r="O10">
-        <v>4386823.878527852</v>
+        <v>3752046.076628235</v>
       </c>
       <c r="P10">
-        <v>17.19891471495537</v>
+        <v>21.49727944871477</v>
       </c>
       <c r="Q10">
-        <v>0.02828170334502245</v>
+        <v>0.03590832571100475</v>
       </c>
       <c r="R10">
-        <v>29.9305083088218</v>
+        <v>31.93687479292505</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F11">
-        <v>101.4509006766775</v>
+        <v>100.9414659787032</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K11">
         <v>4.865822962046021</v>
       </c>
       <c r="L11">
-        <v>11.66666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="M11">
-        <v>7.249328333333335</v>
+        <v>3.4175405</v>
       </c>
       <c r="N11">
         <v>4865822.962046022</v>
       </c>
       <c r="O11">
-        <v>4388358.262485935</v>
+        <v>4653664.262756036</v>
       </c>
       <c r="P11">
-        <v>17.20820406082581</v>
+        <v>17.35257736430469</v>
       </c>
       <c r="Q11">
-        <v>0.02829681846844307</v>
+        <v>0.02881492023384398</v>
       </c>
       <c r="R11">
-        <v>29.92527313790887</v>
+        <v>28.74836051120799</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -3152,55 +3227,55 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C12" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F12">
-        <v>101.2952103697635</v>
+        <v>83.28313600284447</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K12">
         <v>4.865822962046021</v>
       </c>
       <c r="L12">
-        <v>13</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="M12">
-        <v>8.077823</v>
+        <v>10.04549783333334</v>
       </c>
       <c r="N12">
-        <v>4865822.962046022</v>
+        <v>4653664.262756036</v>
       </c>
       <c r="O12">
-        <v>4332154.725287437</v>
+        <v>4194068.255039639</v>
       </c>
       <c r="P12">
-        <v>17.20093755332659</v>
+        <v>15.84899807097114</v>
       </c>
       <c r="Q12">
-        <v>0.02829074084653743</v>
+        <v>0.02639390418649524</v>
       </c>
       <c r="R12">
-        <v>30.11884604087379</v>
+        <v>30.24741485094138</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -3208,55 +3283,55 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F13">
-        <v>101.1201685738514</v>
+        <v>83.28313600284812</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K13">
         <v>4.865822962046021</v>
       </c>
       <c r="L13">
-        <v>2.749999999999996</v>
+        <v>4.333333333333329</v>
       </c>
       <c r="M13">
-        <v>1.708770249999997</v>
+        <v>2.692607666666664</v>
       </c>
       <c r="N13">
-        <v>4865822.962046022</v>
+        <v>4194068.255039639</v>
       </c>
       <c r="O13">
-        <v>4758291.132987313</v>
+        <v>4062261.392273773</v>
       </c>
       <c r="P13">
-        <v>17.02593452642517</v>
+        <v>16.35116712552599</v>
       </c>
       <c r="Q13">
-        <v>0.02795877580565072</v>
+        <v>0.02725385453284113</v>
       </c>
       <c r="R13">
-        <v>28.73844546363172</v>
+        <v>30.72286661121655</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -3264,55 +3339,55 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F14">
-        <v>101.1201685738518</v>
+        <v>83.06433626359167</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K14">
         <v>4.865822962046021</v>
       </c>
       <c r="L14">
-        <v>10.25000000000001</v>
+        <v>11.83333333333334</v>
       </c>
       <c r="M14">
-        <v>6.369052750000007</v>
+        <v>7.35289016666667</v>
       </c>
       <c r="N14">
-        <v>4758291.132987313</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O14">
-        <v>4334063.875616732</v>
+        <v>4550938.782374829</v>
       </c>
       <c r="P14">
-        <v>17.06190833226046</v>
+        <v>14.59452709367391</v>
       </c>
       <c r="Q14">
-        <v>0.02806187853600587</v>
+        <v>0.02425015650204879</v>
       </c>
       <c r="R14">
-        <v>30.11220891532664</v>
+        <v>29.06388092592161</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3320,55 +3395,55 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" t="s">
         <v>154</v>
       </c>
-      <c r="C15" t="s">
-        <v>197</v>
-      </c>
-      <c r="D15" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" t="s">
-        <v>251</v>
-      </c>
       <c r="F15">
-        <v>100.9460934392149</v>
+        <v>83.06433626359176</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K15">
         <v>4.865822962046021</v>
       </c>
       <c r="L15">
-        <v>5.499999999999993</v>
+        <v>14.16666666666666</v>
       </c>
       <c r="M15">
-        <v>3.417540499999995</v>
+        <v>8.802755833333329</v>
       </c>
       <c r="N15">
-        <v>4865822.962046022</v>
+        <v>4550938.782374829</v>
       </c>
       <c r="O15">
-        <v>4649025.388800763</v>
+        <v>4143356.033395752</v>
       </c>
       <c r="P15">
-        <v>17.03517344870409</v>
+        <v>15.99637539695562</v>
       </c>
       <c r="Q15">
-        <v>0.02798535516553314</v>
+        <v>0.02664816916695881</v>
       </c>
       <c r="R15">
-        <v>29.07405083180881</v>
+        <v>30.42771821785542</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -3376,55 +3451,55 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="E16" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F16">
-        <v>83.28776346334328</v>
+        <v>82.87043986625582</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K16">
         <v>4.865822962046021</v>
       </c>
       <c r="L16">
-        <v>7.500000000000014</v>
+        <v>2.000000000000014</v>
       </c>
       <c r="M16">
-        <v>4.660282500000009</v>
+        <v>1.242742000000009</v>
       </c>
       <c r="N16">
-        <v>4649025.388800763</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O16">
-        <v>4436616.732692528</v>
+        <v>4814256.614754738</v>
       </c>
       <c r="P16">
-        <v>14.07704920765324</v>
+        <v>13.78088462736599</v>
       </c>
       <c r="Q16">
-        <v>0.02314389481850114</v>
+        <v>0.02286207025790276</v>
       </c>
       <c r="R16">
-        <v>29.76200893650593</v>
+        <v>28.2751304970017</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3432,55 +3507,55 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D17" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E17" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F17">
-        <v>83.17378270903482</v>
+        <v>82.87043986625604</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K17">
         <v>4.865822962046021</v>
       </c>
       <c r="L17">
-        <v>8.666666666666657</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M17">
-        <v>5.385215333333328</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N17">
-        <v>4865822.962046022</v>
+        <v>4814256.614754738</v>
       </c>
       <c r="O17">
-        <v>4631641.691423165</v>
+        <v>4361439.748082154</v>
       </c>
       <c r="P17">
-        <v>14.07284770864969</v>
+        <v>15.17885917183075</v>
       </c>
       <c r="Q17">
-        <v>0.02312035570568373</v>
+        <v>0.02525075904223706</v>
       </c>
       <c r="R17">
-        <v>29.12853586580796</v>
+        <v>29.67465205265786</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3488,55 +3563,55 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D18" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F18">
-        <v>83.17378270903498</v>
+        <v>82.87043986625601</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K18">
         <v>4.865822962046021</v>
       </c>
       <c r="L18">
-        <v>4.333333333333343</v>
+        <v>7.333333333333314</v>
       </c>
       <c r="M18">
-        <v>2.692607666666673</v>
+        <v>4.556720666666655</v>
       </c>
       <c r="N18">
-        <v>4631641.691423165</v>
+        <v>4361439.748082154</v>
       </c>
       <c r="O18">
-        <v>4509994.746194476</v>
+        <v>4146934.697949531</v>
       </c>
       <c r="P18">
-        <v>14.08551876145169</v>
+        <v>15.94558009565562</v>
       </c>
       <c r="Q18">
-        <v>0.02315157233922331</v>
+        <v>0.02656292549720357</v>
       </c>
       <c r="R18">
-        <v>29.51880405340748</v>
+        <v>30.41488867883603</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -3544,55 +3619,55 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F19">
-        <v>83.08066432305833</v>
+        <v>82.67805381671836</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K19">
         <v>4.865822962046021</v>
       </c>
       <c r="L19">
-        <v>11.83333333333333</v>
+        <v>9.333333333333357</v>
       </c>
       <c r="M19">
-        <v>7.352890166666665</v>
+        <v>5.799462666666681</v>
       </c>
       <c r="N19">
         <v>4865822.962046022</v>
       </c>
       <c r="O19">
-        <v>4543799.617857576</v>
+        <v>4621509.482889677</v>
       </c>
       <c r="P19">
-        <v>14.09418566074473</v>
+        <v>14.30967211131622</v>
       </c>
       <c r="Q19">
-        <v>0.02316294443784727</v>
+        <v>0.0237666269853484</v>
       </c>
       <c r="R19">
-        <v>29.40874899943167</v>
+        <v>28.84600073893219</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -3600,703 +3675,703 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="E20" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F20">
-        <v>83.08066432305816</v>
+        <v>82.67805381671833</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K20">
         <v>4.865822962046021</v>
       </c>
       <c r="L20">
-        <v>1.166666666666671</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M20">
-        <v>0.724932833333336</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N20">
-        <v>4543799.617857576</v>
+        <v>4621509.482889677</v>
       </c>
       <c r="O20">
-        <v>4510805.947256035</v>
+        <v>4150466.938567687</v>
       </c>
       <c r="P20">
-        <v>14.09761694857094</v>
+        <v>15.8953344453365</v>
       </c>
       <c r="Q20">
-        <v>0.0231713884340412</v>
+        <v>0.02647860995759035</v>
       </c>
       <c r="R20">
-        <v>29.5161486245315</v>
+        <v>30.4022414706272</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D21" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F21">
-        <v>82.98787547639479</v>
+        <v>82.48715490056568</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K21">
         <v>4.865822962046021</v>
       </c>
       <c r="L21">
-        <v>13.00000000000001</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M21">
-        <v>8.077823000000008</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N21">
         <v>4865822.962046022</v>
       </c>
       <c r="O21">
-        <v>4511612.992673882</v>
+        <v>4422411.88224749</v>
       </c>
       <c r="P21">
-        <v>14.09216939820492</v>
+        <v>14.90497450231339</v>
       </c>
       <c r="Q21">
-        <v>0.02316236599939102</v>
+        <v>0.02478564732587197</v>
       </c>
       <c r="R21">
-        <v>29.51350750996171</v>
+        <v>29.47395038235064</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D22" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F22">
-        <v>82.89541414527172</v>
+        <v>82.48715490056563</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K22">
         <v>4.865822962046021</v>
       </c>
       <c r="L22">
-        <v>1.999999999999986</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M22">
-        <v>1.242741999999991</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N22">
-        <v>4865822.962046022</v>
+        <v>4422411.88224749</v>
       </c>
       <c r="O22">
-        <v>4813140.542938863</v>
+        <v>3930520.934467885</v>
       </c>
       <c r="P22">
-        <v>13.94877675933988</v>
+        <v>16.72453341327578</v>
       </c>
       <c r="Q22">
-        <v>0.02290101835767783</v>
+        <v>0.02790109074182983</v>
       </c>
       <c r="R22">
-        <v>28.57430053791855</v>
+        <v>31.22121030022013</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="C23" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" t="s">
         <v>205</v>
       </c>
-      <c r="D23" t="s">
-        <v>239</v>
-      </c>
       <c r="E23" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F23">
-        <v>82.89541414527135</v>
+        <v>82.2299199245237</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K23">
         <v>4.865822962046021</v>
       </c>
       <c r="L23">
-        <v>11.00000000000001</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="M23">
-        <v>6.835081000000007</v>
+        <v>10.35618333333333</v>
       </c>
       <c r="N23">
-        <v>4813140.542938863</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O23">
-        <v>4512413.546952056</v>
+        <v>4425244.244656089</v>
       </c>
       <c r="P23">
-        <v>13.98037363450025</v>
+        <v>14.84919438199435</v>
       </c>
       <c r="Q23">
-        <v>0.02297854716720668</v>
+        <v>0.02469245337252757</v>
       </c>
       <c r="R23">
-        <v>29.51088833844473</v>
+        <v>29.46472581385648</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="C24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D24" t="s">
         <v>207</v>
       </c>
       <c r="E24" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F24">
-        <v>82.80327766749903</v>
+        <v>82.22991992452374</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K24">
         <v>4.865822962046021</v>
       </c>
       <c r="L24">
-        <v>5.666666666666657</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M24">
-        <v>3.521102333333328</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N24">
-        <v>4865822.962046022</v>
+        <v>4425244.244656089</v>
       </c>
       <c r="O24">
-        <v>4715361.395697353</v>
+        <v>3936874.337478292</v>
       </c>
       <c r="P24">
-        <v>13.97540309963043</v>
+        <v>16.64612358902679</v>
       </c>
       <c r="Q24">
-        <v>0.02295308105429554</v>
+        <v>0.02776906837155796</v>
       </c>
       <c r="R24">
-        <v>28.86891123773806</v>
+        <v>31.1966180148351</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="C25" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="E25" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F25">
-        <v>82.80327766749905</v>
+        <v>81.97547305970255</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K25">
         <v>4.865822962046021</v>
       </c>
       <c r="L25">
-        <v>7.333333333333343</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M25">
-        <v>4.556720666666672</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N25">
-        <v>4715361.395697353</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O25">
-        <v>4513210.355730941</v>
+        <v>4428035.717958147</v>
       </c>
       <c r="P25">
-        <v>13.99661199420131</v>
+        <v>14.79412078542933</v>
       </c>
       <c r="Q25">
-        <v>0.02300516971012825</v>
+        <v>0.02460044405211842</v>
       </c>
       <c r="R25">
-        <v>29.50828211337421</v>
+        <v>29.45564288414096</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="C26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D26" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E26" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F26">
-        <v>82.71146415244415</v>
+        <v>81.97547305970251</v>
       </c>
       <c r="G26">
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K26">
         <v>4.865822962046021</v>
       </c>
       <c r="L26">
-        <v>9.333333333333329</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M26">
-        <v>5.799462666666664</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N26">
-        <v>4865822.962046022</v>
+        <v>4428035.717958147</v>
       </c>
       <c r="O26">
-        <v>4615950.509760415</v>
+        <v>3943130.128600618</v>
       </c>
       <c r="P26">
-        <v>14.00237447878313</v>
+        <v>16.56892408231841</v>
       </c>
       <c r="Q26">
-        <v>0.02300592722311325</v>
+        <v>0.02763909671695524</v>
       </c>
       <c r="R26">
-        <v>29.17798005668771</v>
+        <v>31.17246025029944</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D27" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="E27" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F27">
-        <v>82.71146415244446</v>
+        <v>81.72375911593898</v>
       </c>
       <c r="G27">
         <v>650</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I27">
         <v>9.525</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K27">
         <v>4.865822962046021</v>
       </c>
       <c r="L27">
-        <v>3.666666666666671</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M27">
-        <v>2.278360333333336</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N27">
-        <v>4615950.509760415</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O27">
-        <v>4514004.5003164</v>
+        <v>4430787.25579149</v>
       </c>
       <c r="P27">
-        <v>14.01305206316068</v>
+        <v>14.73973785961398</v>
       </c>
       <c r="Q27">
-        <v>0.02303212385771408</v>
+        <v>0.02450959271373574</v>
       </c>
       <c r="R27">
-        <v>29.50568528934254</v>
+        <v>29.44669811237342</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D28" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="E28" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F28">
-        <v>82.61997201657491</v>
+        <v>81.72375911593907</v>
       </c>
       <c r="G28">
         <v>650</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I28">
         <v>9.525</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K28">
         <v>4.865822962046021</v>
       </c>
       <c r="L28">
-        <v>13</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M28">
-        <v>8.077823</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N28">
-        <v>4865822.962046022</v>
+        <v>4430787.25579149</v>
       </c>
       <c r="O28">
-        <v>4514797.64512231</v>
+        <v>3949290.725564021</v>
       </c>
       <c r="P28">
-        <v>14.02969571939093</v>
+        <v>16.49290270323301</v>
       </c>
       <c r="Q28">
-        <v>0.02305941255368098</v>
+        <v>0.02751112099382462</v>
       </c>
       <c r="R28">
-        <v>29.50309241872604</v>
+        <v>31.14872485664626</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="C29" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D29" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E29" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F29">
-        <v>82.52880014280876</v>
+        <v>81.47472452362258</v>
       </c>
       <c r="G29">
         <v>650</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I29">
         <v>9.525</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K29">
         <v>4.865822962046021</v>
       </c>
       <c r="L29">
-        <v>16.66666666666667</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="M29">
-        <v>10.35618333333334</v>
+        <v>10.35618333333333</v>
       </c>
       <c r="N29">
         <v>4865822.962046022</v>
       </c>
       <c r="O29">
-        <v>4411780.608969413</v>
+        <v>4433499.780649483</v>
       </c>
       <c r="P29">
-        <v>14.05737182976259</v>
+        <v>14.68603026585134</v>
       </c>
       <c r="Q29">
-        <v>0.02311365814609648</v>
+        <v>0.02441987357279862</v>
       </c>
       <c r="R29">
-        <v>29.84569783487119</v>
+        <v>29.4378881364985</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D30" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="E30" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F30">
-        <v>82.52880014280896</v>
+        <v>81.47472452362251</v>
       </c>
       <c r="G30">
         <v>650</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I30">
         <v>9.525</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K30">
         <v>4.865822962046021</v>
       </c>
       <c r="L30">
-        <v>8.333333333333336</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M30">
-        <v>5.178091666666668</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N30">
-        <v>4411780.608969413</v>
+        <v>4433499.780649483</v>
       </c>
       <c r="O30">
-        <v>4166236.516943549</v>
+        <v>3955358.462512427</v>
       </c>
       <c r="P30">
-        <v>14.08207178792305</v>
+        <v>16.41802847308139</v>
       </c>
       <c r="Q30">
-        <v>0.02317530305451931</v>
+        <v>0.02738508848628615</v>
       </c>
       <c r="R30">
-        <v>30.71301550159657</v>
+        <v>31.12540015040886</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="C31" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D31" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E31" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F31">
-        <v>82.33861846568306</v>
+        <v>81.22831727508509</v>
       </c>
       <c r="G31">
         <v>650</v>
       </c>
       <c r="H31" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I31">
         <v>9.525</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K31">
         <v>4.865822962046021</v>
       </c>
       <c r="L31">
-        <v>8.333333333333332</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M31">
-        <v>5.178091666666666</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N31">
         <v>4865822.962046022</v>
       </c>
       <c r="O31">
-        <v>4645369.168728107</v>
+        <v>4436174.185142362</v>
       </c>
       <c r="P31">
-        <v>13.92768665774181</v>
+        <v>14.63298315897377</v>
       </c>
       <c r="Q31">
-        <v>0.02288069397296717</v>
+        <v>0.02433126167598327</v>
       </c>
       <c r="R31">
-        <v>29.08548498654647</v>
+        <v>29.42920970820802</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
       <c r="C32" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D32" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E32" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="F32">
-        <v>82.33861846568304</v>
+        <v>81.2283172750852</v>
       </c>
       <c r="G32">
         <v>650</v>
       </c>
       <c r="H32" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I32">
         <v>9.525</v>
       </c>
       <c r="J32" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K32">
         <v>4.865822962046021</v>
@@ -4308,691 +4383,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N32">
-        <v>4645369.168728107</v>
+        <v>4436174.185142362</v>
       </c>
       <c r="O32">
-        <v>4169649.008487279</v>
+        <v>3961335.593607123</v>
       </c>
       <c r="P32">
-        <v>13.97607813729472</v>
+        <v>16.34427156721599</v>
       </c>
       <c r="Q32">
-        <v>0.02300057997666824</v>
+        <v>0.02726094844881956</v>
       </c>
       <c r="R32">
-        <v>30.70043171135318</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
-      <c r="A33">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>172</v>
-      </c>
-      <c r="C33" t="s">
-        <v>215</v>
-      </c>
-      <c r="D33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E33" t="s">
-        <v>251</v>
-      </c>
-      <c r="F33">
-        <v>82.14993968860691</v>
-      </c>
-      <c r="G33">
-        <v>650</v>
-      </c>
-      <c r="H33" t="s">
-        <v>86</v>
-      </c>
-      <c r="I33">
-        <v>9.525</v>
-      </c>
-      <c r="J33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K33">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L33">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="M33">
-        <v>10.35618333333333</v>
-      </c>
-      <c r="N33">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O33">
-        <v>4416056.092930035</v>
-      </c>
-      <c r="P33">
-        <v>13.99283942086906</v>
-      </c>
-      <c r="Q33">
-        <v>0.02300718901967778</v>
-      </c>
-      <c r="R33">
-        <v>29.83124066304265</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
-      <c r="A34">
-        <v>2</v>
-      </c>
-      <c r="B34" t="s">
-        <v>173</v>
-      </c>
-      <c r="C34" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" t="s">
-        <v>245</v>
-      </c>
-      <c r="E34" t="s">
-        <v>251</v>
-      </c>
-      <c r="F34">
-        <v>82.14993968860699</v>
-      </c>
-      <c r="G34">
-        <v>650</v>
-      </c>
-      <c r="H34" t="s">
-        <v>86</v>
-      </c>
-      <c r="I34">
-        <v>9.525</v>
-      </c>
-      <c r="J34" t="s">
-        <v>85</v>
-      </c>
-      <c r="K34">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L34">
-        <v>8.333333333333343</v>
-      </c>
-      <c r="M34">
-        <v>5.178091666666672</v>
-      </c>
-      <c r="N34">
-        <v>4416056.092930035</v>
-      </c>
-      <c r="O34">
-        <v>4173025.781469109</v>
-      </c>
-      <c r="P34">
-        <v>14.01742599028097</v>
-      </c>
-      <c r="Q34">
-        <v>0.02306834272901305</v>
-      </c>
-      <c r="R34">
-        <v>30.68799484888891</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
-      <c r="A35">
-        <v>2</v>
-      </c>
-      <c r="B35" t="s">
-        <v>174</v>
-      </c>
-      <c r="C35" t="s">
-        <v>217</v>
-      </c>
-      <c r="D35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E35" t="s">
-        <v>251</v>
-      </c>
-      <c r="F35">
-        <v>81.96274437805975</v>
-      </c>
-      <c r="G35">
-        <v>650</v>
-      </c>
-      <c r="H35" t="s">
-        <v>86</v>
-      </c>
-      <c r="I35">
-        <v>9.525</v>
-      </c>
-      <c r="J35" t="s">
-        <v>85</v>
-      </c>
-      <c r="K35">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L35">
-        <v>8.333333333333329</v>
-      </c>
-      <c r="M35">
-        <v>5.178091666666663</v>
-      </c>
-      <c r="N35">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O35">
-        <v>4647379.598481401</v>
-      </c>
-      <c r="P35">
-        <v>13.86410705666599</v>
-      </c>
-      <c r="Q35">
-        <v>0.02277607272677249</v>
-      </c>
-      <c r="R35">
-        <v>29.07919606870839</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
-      <c r="A36">
-        <v>2</v>
-      </c>
-      <c r="B36" t="s">
-        <v>175</v>
-      </c>
-      <c r="C36" t="s">
-        <v>218</v>
-      </c>
-      <c r="D36" t="s">
-        <v>246</v>
-      </c>
-      <c r="E36" t="s">
-        <v>251</v>
-      </c>
-      <c r="F36">
-        <v>81.96274437805984</v>
-      </c>
-      <c r="G36">
-        <v>650</v>
-      </c>
-      <c r="H36" t="s">
-        <v>86</v>
-      </c>
-      <c r="I36">
-        <v>9.525</v>
-      </c>
-      <c r="J36" t="s">
-        <v>85</v>
-      </c>
-      <c r="K36">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L36">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M36">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N36">
-        <v>4647379.598481401</v>
-      </c>
-      <c r="O36">
-        <v>4176364.41761048</v>
-      </c>
-      <c r="P36">
-        <v>13.91227763011719</v>
-      </c>
-      <c r="Q36">
-        <v>0.02289502257904661</v>
-      </c>
-      <c r="R36">
-        <v>30.67571329440749</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
-      <c r="A37">
-        <v>3</v>
-      </c>
-      <c r="B37" t="s">
-        <v>176</v>
-      </c>
-      <c r="C37" t="s">
-        <v>219</v>
-      </c>
-      <c r="D37" t="s">
-        <v>220</v>
-      </c>
-      <c r="E37" t="s">
-        <v>251</v>
-      </c>
-      <c r="F37">
-        <v>81.77701252674811</v>
-      </c>
-      <c r="G37">
-        <v>650</v>
-      </c>
-      <c r="H37" t="s">
-        <v>86</v>
-      </c>
-      <c r="I37">
-        <v>9.525</v>
-      </c>
-      <c r="J37" t="s">
-        <v>85</v>
-      </c>
-      <c r="K37">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L37">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M37">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N37">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O37">
-        <v>4420241.945999204</v>
-      </c>
-      <c r="P37">
-        <v>13.92931764700834</v>
-      </c>
-      <c r="Q37">
-        <v>0.02290239253705801</v>
-      </c>
-      <c r="R37">
-        <v>29.81710690382073</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
-      <c r="A38">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
-        <v>177</v>
-      </c>
-      <c r="C38" t="s">
-        <v>220</v>
-      </c>
-      <c r="D38" t="s">
-        <v>247</v>
-      </c>
-      <c r="E38" t="s">
-        <v>251</v>
-      </c>
-      <c r="F38">
-        <v>81.77701252674824</v>
-      </c>
-      <c r="G38">
-        <v>650</v>
-      </c>
-      <c r="H38" t="s">
-        <v>86</v>
-      </c>
-      <c r="I38">
-        <v>9.525</v>
-      </c>
-      <c r="J38" t="s">
-        <v>85</v>
-      </c>
-      <c r="K38">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L38">
-        <v>8.333333333333336</v>
-      </c>
-      <c r="M38">
-        <v>5.178091666666668</v>
-      </c>
-      <c r="N38">
-        <v>4420241.945999204</v>
-      </c>
-      <c r="O38">
-        <v>4179668.383327221</v>
-      </c>
-      <c r="P38">
-        <v>13.95379260344057</v>
-      </c>
-      <c r="Q38">
-        <v>0.02296306612917482</v>
-      </c>
-      <c r="R38">
-        <v>30.66357378413788</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
-      <c r="A39">
-        <v>3</v>
-      </c>
-      <c r="B39" t="s">
-        <v>178</v>
-      </c>
-      <c r="C39" t="s">
-        <v>221</v>
-      </c>
-      <c r="D39" t="s">
-        <v>222</v>
-      </c>
-      <c r="E39" t="s">
-        <v>251</v>
-      </c>
-      <c r="F39">
-        <v>81.5927253830228</v>
-      </c>
-      <c r="G39">
-        <v>650</v>
-      </c>
-      <c r="H39" t="s">
-        <v>86</v>
-      </c>
-      <c r="I39">
-        <v>9.525</v>
-      </c>
-      <c r="J39" t="s">
-        <v>85</v>
-      </c>
-      <c r="K39">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L39">
-        <v>8.333333333333332</v>
-      </c>
-      <c r="M39">
-        <v>5.178091666666666</v>
-      </c>
-      <c r="N39">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O39">
-        <v>4649349.139201025</v>
-      </c>
-      <c r="P39">
-        <v>13.80151785227662</v>
-      </c>
-      <c r="Q39">
-        <v>0.02267308355916841</v>
-      </c>
-      <c r="R39">
-        <v>29.07303901185268</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
-      <c r="A40">
-        <v>3</v>
-      </c>
-      <c r="B40" t="s">
-        <v>179</v>
-      </c>
-      <c r="C40" t="s">
-        <v>222</v>
-      </c>
-      <c r="D40" t="s">
-        <v>248</v>
-      </c>
-      <c r="E40" t="s">
-        <v>251</v>
-      </c>
-      <c r="F40">
-        <v>81.59272538302294</v>
-      </c>
-      <c r="G40">
-        <v>650</v>
-      </c>
-      <c r="H40" t="s">
-        <v>86</v>
-      </c>
-      <c r="I40">
-        <v>9.525</v>
-      </c>
-      <c r="J40" t="s">
-        <v>85</v>
-      </c>
-      <c r="K40">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L40">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M40">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N40">
-        <v>4649349.139201025</v>
-      </c>
-      <c r="O40">
-        <v>4182935.604321522</v>
-      </c>
-      <c r="P40">
-        <v>13.84947096074036</v>
-      </c>
-      <c r="Q40">
-        <v>0.0227911178983025</v>
-      </c>
-      <c r="R40">
-        <v>30.65158344372771</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41">
-        <v>3</v>
-      </c>
-      <c r="B41" t="s">
-        <v>180</v>
-      </c>
-      <c r="C41" t="s">
-        <v>223</v>
-      </c>
-      <c r="D41" t="s">
-        <v>224</v>
-      </c>
-      <c r="E41" t="s">
-        <v>251</v>
-      </c>
-      <c r="F41">
-        <v>81.40986372308849</v>
-      </c>
-      <c r="G41">
-        <v>650</v>
-      </c>
-      <c r="H41" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41">
-        <v>9.525</v>
-      </c>
-      <c r="J41" t="s">
-        <v>85</v>
-      </c>
-      <c r="K41">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L41">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="M41">
-        <v>10.35618333333333</v>
-      </c>
-      <c r="N41">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O41">
-        <v>4424341.028821101</v>
-      </c>
-      <c r="P41">
-        <v>13.86678011779473</v>
-      </c>
-      <c r="Q41">
-        <v>0.02279922488271709</v>
-      </c>
-      <c r="R41">
-        <v>29.80328557989864</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>181</v>
-      </c>
-      <c r="C42" t="s">
-        <v>224</v>
-      </c>
-      <c r="D42" t="s">
-        <v>249</v>
-      </c>
-      <c r="E42" t="s">
-        <v>251</v>
-      </c>
-      <c r="F42">
-        <v>81.40986372308849</v>
-      </c>
-      <c r="G42">
-        <v>650</v>
-      </c>
-      <c r="H42" t="s">
-        <v>86</v>
-      </c>
-      <c r="I42">
-        <v>9.525</v>
-      </c>
-      <c r="J42" t="s">
-        <v>85</v>
-      </c>
-      <c r="K42">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L42">
-        <v>8.333333333333343</v>
-      </c>
-      <c r="M42">
-        <v>5.178091666666672</v>
-      </c>
-      <c r="N42">
-        <v>4424341.028821101</v>
-      </c>
-      <c r="O42">
-        <v>4186169.152985218</v>
-      </c>
-      <c r="P42">
-        <v>13.89114519064601</v>
-      </c>
-      <c r="Q42">
-        <v>0.02285942357653978</v>
-      </c>
-      <c r="R42">
-        <v>30.63973785249047</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43">
-        <v>3</v>
-      </c>
-      <c r="B43" t="s">
-        <v>182</v>
-      </c>
-      <c r="C43" t="s">
-        <v>225</v>
-      </c>
-      <c r="D43" t="s">
-        <v>226</v>
-      </c>
-      <c r="E43" t="s">
-        <v>251</v>
-      </c>
-      <c r="F43">
-        <v>81.2283172750852</v>
-      </c>
-      <c r="G43">
-        <v>650</v>
-      </c>
-      <c r="H43" t="s">
-        <v>86</v>
-      </c>
-      <c r="I43">
-        <v>9.525</v>
-      </c>
-      <c r="J43" t="s">
-        <v>85</v>
-      </c>
-      <c r="K43">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L43">
-        <v>8.333333333333329</v>
-      </c>
-      <c r="M43">
-        <v>5.178091666666663</v>
-      </c>
-      <c r="N43">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O43">
-        <v>4651279.543866448</v>
-      </c>
-      <c r="P43">
-        <v>13.73987773689126</v>
-      </c>
-      <c r="Q43">
-        <v>0.02257165837799355</v>
-      </c>
-      <c r="R43">
-        <v>29.06700809331659</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
-      <c r="A44">
-        <v>3</v>
-      </c>
-      <c r="B44" t="s">
-        <v>183</v>
-      </c>
-      <c r="C44" t="s">
-        <v>226</v>
-      </c>
-      <c r="D44" t="s">
-        <v>250</v>
-      </c>
-      <c r="E44" t="s">
-        <v>251</v>
-      </c>
-      <c r="F44">
-        <v>81.22831727508516</v>
-      </c>
-      <c r="G44">
-        <v>650</v>
-      </c>
-      <c r="H44" t="s">
-        <v>86</v>
-      </c>
-      <c r="I44">
-        <v>9.525</v>
-      </c>
-      <c r="J44" t="s">
-        <v>85</v>
-      </c>
-      <c r="K44">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L44">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M44">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N44">
-        <v>4651279.543866448</v>
-      </c>
-      <c r="O44">
-        <v>4189368.912780208</v>
-      </c>
-      <c r="P44">
-        <v>13.787616677959</v>
-      </c>
-      <c r="Q44">
-        <v>0.02268878607000538</v>
-      </c>
-      <c r="R44">
-        <v>30.62802960165667</v>
+        <v>31.10247489231902</v>
       </c>
     </row>
   </sheetData>
@@ -5002,63 +4405,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>263</v>
+      <c r="C1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" t="s">
+        <v>235</v>
+      </c>
+      <c r="O1" t="s">
+        <v>236</v>
+      </c>
+      <c r="P1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>238</v>
+      </c>
+      <c r="R1" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -5066,40 +4469,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F2">
-        <v>11.66666666666667</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="G2">
-        <v>7.249328333333333</v>
+        <v>14.49865666666667</v>
       </c>
       <c r="H2">
-        <v>1.110758181499602</v>
+        <v>1.261102509788969</v>
       </c>
       <c r="I2">
-        <v>35.48634805525908</v>
+        <v>77.28025445914412</v>
       </c>
       <c r="J2">
-        <v>3.712822449268846</v>
+        <v>8.085584439241739</v>
       </c>
       <c r="K2">
-        <v>4978.969160918507</v>
+        <v>10842.93044471196</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>3.712822449268846</v>
+        <v>8.085584439241739</v>
       </c>
       <c r="N2">
         <v>0.78</v>
@@ -5108,13 +4511,13 @@
         <v>0.357</v>
       </c>
       <c r="P2">
-        <v>12106254.18251517</v>
+        <v>18684989.6627345</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>12106254.18251517</v>
+        <v>18684989.6627345</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5122,40 +4525,40 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F3">
-        <v>23.33333333333333</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="G3">
-        <v>14.49865666666667</v>
+        <v>28.99731333333333</v>
       </c>
       <c r="H3">
-        <v>1.110362571501391</v>
+        <v>1.258641544553011</v>
       </c>
       <c r="I3">
-        <v>35.30907469415853</v>
+        <v>76.35279733482363</v>
       </c>
       <c r="J3">
-        <v>3.694274907726207</v>
+        <v>7.988547583644502</v>
       </c>
       <c r="K3">
-        <v>4954.096536758998</v>
+        <v>10712.80208061895</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>3.694274907726207</v>
+        <v>7.988547583644502</v>
       </c>
       <c r="N3">
         <v>0.78</v>
@@ -5164,54 +4567,51 @@
         <v>0.357</v>
       </c>
       <c r="P3">
-        <v>12078987.97075614</v>
+        <v>18535748.53236309</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>12078987.97075614</v>
+        <v>18535748.53236309</v>
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4">
-        <v>0</v>
-      </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>264</v>
+        <v>154</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G4">
-        <v>21.747985</v>
+        <v>43.49597</v>
       </c>
       <c r="H4">
-        <v>1.109969521856537</v>
+        <v>1.256228622534425</v>
       </c>
       <c r="I4">
-        <v>35.13313034723929</v>
+        <v>75.44491389486112</v>
       </c>
       <c r="J4">
-        <v>3.675866416662363</v>
+        <v>7.893558659679624</v>
       </c>
       <c r="K4">
-        <v>4929.410382072562</v>
+        <v>10585.42003380357</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>3.675866416662363</v>
+        <v>12.5</v>
       </c>
       <c r="N4">
         <v>0.78</v>
@@ -5220,54 +4620,54 @@
         <v>0.357</v>
       </c>
       <c r="P4">
-        <v>12051931.50382208</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R4">
-        <v>12051931.50382208</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F5">
-        <v>46.66666666666666</v>
+        <v>96</v>
       </c>
       <c r="G5">
-        <v>28.99731333333333</v>
+        <v>59.651616</v>
       </c>
       <c r="H5">
-        <v>1.109578922612094</v>
+        <v>1.296845204635301</v>
       </c>
       <c r="I5">
-        <v>34.95849920270307</v>
+        <v>85.98355850964867</v>
       </c>
       <c r="J5">
-        <v>3.65759532173972</v>
+        <v>8.996183146418002</v>
       </c>
       <c r="K5">
-        <v>4904.9084783594</v>
+        <v>12064.06152300947</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>3.65759532173972</v>
+        <v>8.996183146418002</v>
       </c>
       <c r="N5">
         <v>0.78</v>
@@ -5276,54 +4676,54 @@
         <v>0.357</v>
       </c>
       <c r="P5">
-        <v>12025082.23056671</v>
+        <v>20092665.5797895</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>12025082.23056671</v>
+        <v>20092665.5797895</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F6">
-        <v>58.33333333333333</v>
+        <v>122</v>
       </c>
       <c r="G6">
-        <v>36.24664166666666</v>
+        <v>75.80726199999999</v>
       </c>
       <c r="H6">
-        <v>1.109190406722896</v>
+        <v>1.197811389316449</v>
       </c>
       <c r="I6">
-        <v>34.785064704352</v>
+        <v>48.64260650466742</v>
       </c>
       <c r="J6">
-        <v>3.639449428058218</v>
+        <v>5.089319451532429</v>
       </c>
       <c r="K6">
-        <v>4880.574472014631</v>
+        <v>6824.879170894018</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>3.639449428058218</v>
+        <v>5.089319451532429</v>
       </c>
       <c r="N6">
         <v>0.78</v>
@@ -5332,51 +4732,54 @@
         <v>0.357</v>
       </c>
       <c r="P6">
-        <v>11998422.11784048</v>
+        <v>14144849.90860312</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>11998422.11784048</v>
+        <v>14144849.90860312</v>
       </c>
     </row>
     <row r="7" spans="1:18">
+      <c r="A7">
+        <v>1</v>
+      </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="F7">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="G7">
-        <v>43.49597</v>
+        <v>91.962908</v>
       </c>
       <c r="H7">
-        <v>1.108802579689474</v>
+        <v>1.174367571318306</v>
       </c>
       <c r="I7">
-        <v>34.61239277122915</v>
+        <v>43.10620380754742</v>
       </c>
       <c r="J7">
-        <v>3.621383319123625</v>
+        <v>4.510063446094772</v>
       </c>
       <c r="K7">
-        <v>4856.347458611163</v>
+        <v>6048.085282482011</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>12.5</v>
+        <v>4.510063446094772</v>
       </c>
       <c r="N7">
         <v>0.78</v>
@@ -5385,13 +4788,13 @@
         <v>0.357</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>13283351.63135838</v>
       </c>
       <c r="Q7">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>16916025.69007904</v>
+        <v>13283351.63135838</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -5399,40 +4802,40 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F8">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="G8">
-        <v>51.573793</v>
+        <v>108.118554</v>
       </c>
       <c r="H8">
-        <v>1.123187713874457</v>
+        <v>1.173354131776405</v>
       </c>
       <c r="I8">
-        <v>38.91453085954409</v>
+        <v>42.77042985275748</v>
       </c>
       <c r="J8">
-        <v>4.071502188759833</v>
+        <v>4.474932497277989</v>
       </c>
       <c r="K8">
-        <v>5459.965865170711</v>
+        <v>6000.973977499729</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>4.071502188759833</v>
+        <v>4.474932497277989</v>
       </c>
       <c r="N8">
         <v>0.78</v>
@@ -5441,54 +4844,51 @@
         <v>0.357</v>
       </c>
       <c r="P8">
-        <v>12634599.23977768</v>
+        <v>13231272.26718051</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>12634599.23977768</v>
+        <v>13231272.26718051</v>
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9">
-        <v>1</v>
-      </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="D9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E9" t="s">
-        <v>264</v>
+        <v>154</v>
       </c>
       <c r="F9">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="G9">
-        <v>59.651616</v>
+        <v>124.2742</v>
       </c>
       <c r="H9">
-        <v>1.122692950932483</v>
+        <v>1.17235555277672</v>
       </c>
       <c r="I9">
-        <v>38.69962688738584</v>
+        <v>42.43981682607586</v>
       </c>
       <c r="J9">
-        <v>4.04901747742736</v>
+        <v>4.440341519768192</v>
       </c>
       <c r="K9">
-        <v>5429.813417579639</v>
+        <v>5954.586784839541</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>4.04901747742736</v>
+        <v>12.5</v>
       </c>
       <c r="N9">
         <v>0.78</v>
@@ -5497,54 +4897,54 @@
         <v>0.357</v>
       </c>
       <c r="P9">
-        <v>12601419.4133833</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R9">
-        <v>12601419.4133833</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F10">
-        <v>109</v>
+        <v>233.3333333333333</v>
       </c>
       <c r="G10">
-        <v>67.72943900000001</v>
+        <v>144.9865666666667</v>
       </c>
       <c r="H10">
-        <v>1.096741786639076</v>
+        <v>1.237958795582591</v>
       </c>
       <c r="I10">
-        <v>25.33970559941271</v>
+        <v>57.18736116736668</v>
       </c>
       <c r="J10">
-        <v>2.651211887480207</v>
+        <v>5.983329646263154</v>
       </c>
       <c r="K10">
-        <v>3555.328165348707</v>
+        <v>8023.764722231816</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>2.651211887480207</v>
+        <v>5.983329646263154</v>
       </c>
       <c r="N10">
         <v>0.78</v>
@@ -5553,54 +4953,54 @@
         <v>0.357</v>
       </c>
       <c r="P10">
-        <v>10554287.48727263</v>
+        <v>15484786.78923609</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>10554287.48727263</v>
+        <v>15484786.78923609</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F11">
-        <v>122</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="G11">
-        <v>75.80726200000001</v>
+        <v>165.6989333333333</v>
       </c>
       <c r="H11">
-        <v>1.078897700746058</v>
+        <v>1.235960954030032</v>
       </c>
       <c r="I11">
-        <v>20.70167460157071</v>
+        <v>56.56752040616683</v>
       </c>
       <c r="J11">
-        <v>2.165949623175708</v>
+        <v>5.918477701239929</v>
       </c>
       <c r="K11">
-        <v>2904.581763671088</v>
+        <v>7936.796966916769</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2.165949623175708</v>
+        <v>5.918477701239929</v>
       </c>
       <c r="N11">
         <v>0.78</v>
@@ -5609,54 +5009,51 @@
         <v>0.357</v>
       </c>
       <c r="P11">
-        <v>9953691.026075777</v>
+        <v>15387165.75339465</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>9953691.026075777</v>
+        <v>15387165.75339465</v>
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12">
-        <v>1</v>
-      </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
-        <v>264</v>
+        <v>154</v>
       </c>
       <c r="F12">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="G12">
-        <v>83.885085</v>
+        <v>186.4113</v>
       </c>
       <c r="H12">
-        <v>1.078703677112501</v>
+        <v>1.234000097220443</v>
       </c>
       <c r="I12">
-        <v>20.62841285465433</v>
+        <v>55.95994928201454</v>
       </c>
       <c r="J12">
-        <v>2.158284482254466</v>
+        <v>5.854909488873656</v>
       </c>
       <c r="K12">
-        <v>2894.302656392884</v>
+        <v>7851.550722769351</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>2.158284482254466</v>
+        <v>12.5</v>
       </c>
       <c r="N12">
         <v>0.78</v>
@@ -5665,54 +5062,54 @@
         <v>0.357</v>
       </c>
       <c r="P12">
-        <v>9953691.026075777</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R12">
-        <v>9953691.026075777</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="E13" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F13">
-        <v>148</v>
+        <v>333.3333333333333</v>
       </c>
       <c r="G13">
-        <v>91.96290800000001</v>
+        <v>207.1236666666667</v>
       </c>
       <c r="H13">
-        <v>1.078510716665485</v>
+        <v>1.23207514973492</v>
       </c>
       <c r="I13">
-        <v>20.55560102404852</v>
+        <v>55.36428752070728</v>
       </c>
       <c r="J13">
-        <v>2.15066641462957</v>
+        <v>5.792587314833412</v>
       </c>
       <c r="K13">
-        <v>2884.086675346545</v>
+        <v>7767.975440937902</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2.15066641462957</v>
+        <v>5.792587314833412</v>
       </c>
       <c r="N13">
         <v>0.78</v>
@@ -5721,54 +5118,54 @@
         <v>0.357</v>
       </c>
       <c r="P13">
-        <v>9953691.026075777</v>
+        <v>15197852.27000845</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13">
-        <v>9953691.026075777</v>
+        <v>15197852.27000845</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="F14">
-        <v>161</v>
+        <v>366.6666666666667</v>
       </c>
       <c r="G14">
-        <v>100.040731</v>
+        <v>227.8360333333333</v>
       </c>
       <c r="H14">
-        <v>1.07831937640837</v>
+        <v>1.230185078839927</v>
       </c>
       <c r="I14">
-        <v>20.48338103991817</v>
+        <v>54.78018787799369</v>
       </c>
       <c r="J14">
-        <v>2.143110269997627</v>
+        <v>5.731474848070139</v>
       </c>
       <c r="K14">
-        <v>2873.953734272217</v>
+        <v>7686.022400759018</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2.143110269997627</v>
+        <v>5.731474848070139</v>
       </c>
       <c r="N14">
         <v>0.78</v>
@@ -5777,567 +5174,13 @@
         <v>0.357</v>
       </c>
       <c r="P14">
-        <v>9953691.026075777</v>
+        <v>15106041.12364851</v>
       </c>
       <c r="Q14">
         <v>0</v>
       </c>
       <c r="R14">
-        <v>9953691.026075777</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" t="s">
-        <v>240</v>
-      </c>
-      <c r="D15" t="s">
-        <v>208</v>
-      </c>
-      <c r="E15" t="s">
-        <v>264</v>
-      </c>
-      <c r="F15">
-        <v>174</v>
-      </c>
-      <c r="G15">
-        <v>108.118554</v>
-      </c>
-      <c r="H15">
-        <v>1.078128998766328</v>
-      </c>
-      <c r="I15">
-        <v>20.41158137311636</v>
-      </c>
-      <c r="J15">
-        <v>2.135598101815749</v>
-      </c>
-      <c r="K15">
-        <v>2863.879766496955</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>2.135598101815749</v>
-      </c>
-      <c r="N15">
-        <v>0.78</v>
-      </c>
-      <c r="O15">
-        <v>0.357</v>
-      </c>
-      <c r="P15">
-        <v>9953691.026075777</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>9953691.026075777</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" t="s">
-        <v>241</v>
-      </c>
-      <c r="D16" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" t="s">
-        <v>264</v>
-      </c>
-      <c r="F16">
-        <v>187</v>
-      </c>
-      <c r="G16">
-        <v>116.196377</v>
-      </c>
-      <c r="H16">
-        <v>1.077939324540984</v>
-      </c>
-      <c r="I16">
-        <v>20.34013375024011</v>
-      </c>
-      <c r="J16">
-        <v>2.128122766857393</v>
-      </c>
-      <c r="K16">
-        <v>2853.855192811102</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>2.128122766857393</v>
-      </c>
-      <c r="N16">
-        <v>0.78</v>
-      </c>
-      <c r="O16">
-        <v>0.357</v>
-      </c>
-      <c r="P16">
-        <v>9953691.026075777</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>9953691.026075777</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="B17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" t="s">
-        <v>242</v>
-      </c>
-      <c r="D17" t="s">
-        <v>211</v>
-      </c>
-      <c r="E17" t="s">
-        <v>251</v>
-      </c>
-      <c r="F17">
-        <v>200</v>
-      </c>
-      <c r="G17">
-        <v>124.2742</v>
-      </c>
-      <c r="H17">
-        <v>1.077749955704649</v>
-      </c>
-      <c r="I17">
-        <v>20.26893447226658</v>
-      </c>
-      <c r="J17">
-        <v>2.120673415427367</v>
-      </c>
-      <c r="K17">
-        <v>2843.865463556408</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>12.5</v>
-      </c>
-      <c r="N17">
-        <v>0.78</v>
-      </c>
-      <c r="O17">
-        <v>0.357</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R17">
-        <v>16916025.69007904</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" t="s">
-        <v>243</v>
-      </c>
-      <c r="D18" t="s">
-        <v>213</v>
-      </c>
-      <c r="E18" t="s">
-        <v>264</v>
-      </c>
-      <c r="F18">
-        <v>225</v>
-      </c>
-      <c r="G18">
-        <v>139.808475</v>
-      </c>
-      <c r="H18">
-        <v>1.167918082004549</v>
-      </c>
-      <c r="I18">
-        <v>42.28036336486285</v>
-      </c>
-      <c r="J18">
-        <v>4.42365841703011</v>
-      </c>
-      <c r="K18">
-        <v>5932.214410405718</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>4.42365841703011</v>
-      </c>
-      <c r="N18">
-        <v>0.78</v>
-      </c>
-      <c r="O18">
-        <v>0.357</v>
-      </c>
-      <c r="P18">
-        <v>13155296.46749666</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>13155296.46749666</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="B19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" t="s">
-        <v>244</v>
-      </c>
-      <c r="D19" t="s">
-        <v>215</v>
-      </c>
-      <c r="E19" t="s">
-        <v>264</v>
-      </c>
-      <c r="F19">
-        <v>250</v>
-      </c>
-      <c r="G19">
-        <v>155.34275</v>
-      </c>
-      <c r="H19">
-        <v>1.166962243618513</v>
-      </c>
-      <c r="I19">
-        <v>41.94624516190274</v>
-      </c>
-      <c r="J19">
-        <v>4.38870070420128</v>
-      </c>
-      <c r="K19">
-        <v>5885.335418348</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>4.38870070420128</v>
-      </c>
-      <c r="N19">
-        <v>0.78</v>
-      </c>
-      <c r="O19">
-        <v>0.357</v>
-      </c>
-      <c r="P19">
-        <v>13103521.20300996</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>13103521.20300996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" t="s">
-        <v>245</v>
-      </c>
-      <c r="D20" t="s">
-        <v>217</v>
-      </c>
-      <c r="E20" t="s">
-        <v>264</v>
-      </c>
-      <c r="F20">
-        <v>275.0000000000001</v>
-      </c>
-      <c r="G20">
-        <v>170.877025</v>
-      </c>
-      <c r="H20">
-        <v>1.166017948811477</v>
-      </c>
-      <c r="I20">
-        <v>41.6164473347259</v>
-      </c>
-      <c r="J20">
-        <v>4.354195018393445</v>
-      </c>
-      <c r="K20">
-        <v>5839.062603565977</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>4.354195018393445</v>
-      </c>
-      <c r="N20">
-        <v>0.78</v>
-      </c>
-      <c r="O20">
-        <v>0.357</v>
-      </c>
-      <c r="P20">
-        <v>13052434.20924805</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>13052434.20924805</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="B21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D21" t="s">
-        <v>219</v>
-      </c>
-      <c r="E21" t="s">
-        <v>251</v>
-      </c>
-      <c r="F21">
-        <v>300.0000000000001</v>
-      </c>
-      <c r="G21">
-        <v>186.4113</v>
-      </c>
-      <c r="H21">
-        <v>1.165085819984554</v>
-      </c>
-      <c r="I21">
-        <v>41.29109744202606</v>
-      </c>
-      <c r="J21">
-        <v>4.320154705662414</v>
-      </c>
-      <c r="K21">
-        <v>5793.413863387411</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>12.5</v>
-      </c>
-      <c r="N21">
-        <v>0.78</v>
-      </c>
-      <c r="O21">
-        <v>0.357</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R21">
-        <v>16916025.69007904</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" t="s">
-        <v>247</v>
-      </c>
-      <c r="D22" t="s">
-        <v>221</v>
-      </c>
-      <c r="E22" t="s">
-        <v>264</v>
-      </c>
-      <c r="F22">
-        <v>325.0000000000001</v>
-      </c>
-      <c r="G22">
-        <v>201.945575</v>
-      </c>
-      <c r="H22">
-        <v>1.164164836965508</v>
-      </c>
-      <c r="I22">
-        <v>40.9699163344204</v>
-      </c>
-      <c r="J22">
-        <v>4.286550559506197</v>
-      </c>
-      <c r="K22">
-        <v>5748.350031309</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>4.286550559506197</v>
-      </c>
-      <c r="N22">
-        <v>0.78</v>
-      </c>
-      <c r="O22">
-        <v>0.357</v>
-      </c>
-      <c r="P22">
-        <v>12952338.13256341</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>12952338.13256341</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E23" t="s">
-        <v>264</v>
-      </c>
-      <c r="F23">
-        <v>350.0000000000001</v>
-      </c>
-      <c r="G23">
-        <v>217.47985</v>
-      </c>
-      <c r="H23">
-        <v>1.16325552729499</v>
-      </c>
-      <c r="I23">
-        <v>40.65300897739369</v>
-      </c>
-      <c r="J23">
-        <v>4.253393562125825</v>
-      </c>
-      <c r="K23">
-        <v>5703.885834681973</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>4.253393562125825</v>
-      </c>
-      <c r="N23">
-        <v>0.78</v>
-      </c>
-      <c r="O23">
-        <v>0.357</v>
-      </c>
-      <c r="P23">
-        <v>12903300.65253028</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>12903300.65253028</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" t="s">
-        <v>249</v>
-      </c>
-      <c r="D24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E24" t="s">
-        <v>264</v>
-      </c>
-      <c r="F24">
-        <v>375.0000000000001</v>
-      </c>
-      <c r="G24">
-        <v>233.014125</v>
-      </c>
-      <c r="H24">
-        <v>1.162356986596237</v>
-      </c>
-      <c r="I24">
-        <v>40.36061678067849</v>
-      </c>
-      <c r="J24">
-        <v>4.222801507111746</v>
-      </c>
-      <c r="K24">
-        <v>5662.861277066993</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>4.222801507111746</v>
-      </c>
-      <c r="N24">
-        <v>0.78</v>
-      </c>
-      <c r="O24">
-        <v>0.357</v>
-      </c>
-      <c r="P24">
-        <v>12858071.87062018</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>12858071.87062018</v>
+        <v>15106041.12364851</v>
       </c>
     </row>
   </sheetData>
@@ -6347,20 +5190,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>266</v>
+      <c r="A1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="B2">
         <v>4865822.962046022</v>
@@ -6368,191 +5211,191 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="B3">
-        <v>4380632.115152928</v>
+        <v>4318363.853382817</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="B4">
-        <v>4865822.962046022</v>
+        <v>3858388.135997178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B5">
-        <v>4799715.335512225</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="B6">
-        <v>4382192.886298967</v>
+        <v>4735652.057229326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="B7">
-        <v>4865822.962046022</v>
+        <v>4175545.321476262</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B8">
-        <v>4733096.700577617</v>
+        <v>3865932.268884428</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="B9">
-        <v>4383744.658058213</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="B10">
-        <v>4865822.962046022</v>
+        <v>4535819.686219067</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="B11">
-        <v>4665941.396452308</v>
+        <v>3873357.822582715</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="B12">
-        <v>4385287.844681869</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B13">
-        <v>4865822.962046022</v>
+        <v>4225517.642759564</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="B14">
-        <v>4528854.089399976</v>
+        <v>3752046.076628235</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="B15">
-        <v>4386823.878527852</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B16">
-        <v>4865822.962046022</v>
+        <v>4653664.262756036</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="B17">
-        <v>4388358.262485935</v>
+        <v>4194068.255039639</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B18">
-        <v>4865822.962046022</v>
+        <v>4062261.392273773</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="B19">
-        <v>4332154.725287437</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B20">
-        <v>4865822.962046022</v>
+        <v>4550938.782374829</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B21">
-        <v>4758291.132987313</v>
+        <v>4143356.033395752</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="B22">
-        <v>4334063.875616732</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B23">
-        <v>4865822.962046022</v>
+        <v>4814256.614754738</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B24">
-        <v>4649025.388800763</v>
+        <v>4361439.748082154</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="B25">
-        <v>4436616.732692528</v>
+        <v>4146934.697949531</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B26">
         <v>4865822.962046022</v>
@@ -6560,23 +5403,23 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B27">
-        <v>4631641.691423165</v>
+        <v>4621509.482889677</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="B28">
-        <v>4509994.746194476</v>
+        <v>4150466.938567687</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B29">
         <v>4865822.962046022</v>
@@ -6584,39 +5427,39 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B30">
-        <v>4543799.617857576</v>
+        <v>4422411.88224749</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="B31">
-        <v>4510805.947256035</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B32">
-        <v>4865822.962046022</v>
+        <v>3930520.934467885</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="B33">
-        <v>4511612.992673882</v>
+        <v>4425244.244656089</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B34">
         <v>4865822.962046022</v>
@@ -6624,47 +5467,47 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B35">
-        <v>4813140.542938863</v>
+        <v>3936874.337478292</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="B36">
-        <v>4512413.546952056</v>
+        <v>4428035.717958147</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B37">
-        <v>4865822.962046022</v>
+        <v>3943130.128600618</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B38">
-        <v>4715361.395697353</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="B39">
-        <v>4513210.355730941</v>
+        <v>4430787.25579149</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B40">
         <v>4865822.962046022</v>
@@ -6672,23 +5515,23 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B41">
-        <v>4615950.509760415</v>
+        <v>3949290.725564021</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="B42">
-        <v>4514004.5003164</v>
+        <v>4433499.780649483</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="B43">
         <v>4865822.962046022</v>
@@ -6696,202 +5539,26 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="B44">
-        <v>4514797.64512231</v>
+        <v>3955358.462512427</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B45">
-        <v>4865822.962046022</v>
+        <v>4436174.185142362</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="B46">
-        <v>4411780.608969413</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>243</v>
-      </c>
-      <c r="B47">
-        <v>4166236.516943549</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>213</v>
-      </c>
-      <c r="B48">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>214</v>
-      </c>
-      <c r="B49">
-        <v>4645369.168728107</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>244</v>
-      </c>
-      <c r="B50">
-        <v>4169649.008487279</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>215</v>
-      </c>
-      <c r="B51">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>216</v>
-      </c>
-      <c r="B52">
-        <v>4416056.092930035</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>245</v>
-      </c>
-      <c r="B53">
-        <v>4173025.781469109</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>217</v>
-      </c>
-      <c r="B54">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>218</v>
-      </c>
-      <c r="B55">
-        <v>4647379.598481401</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>246</v>
-      </c>
-      <c r="B56">
-        <v>4176364.41761048</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>219</v>
-      </c>
-      <c r="B57">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>220</v>
-      </c>
-      <c r="B58">
-        <v>4420241.945999204</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>247</v>
-      </c>
-      <c r="B59">
-        <v>4179668.383327221</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>221</v>
-      </c>
-      <c r="B60">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>222</v>
-      </c>
-      <c r="B61">
-        <v>4649349.139201025</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>248</v>
-      </c>
-      <c r="B62">
-        <v>4182935.604321522</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>223</v>
-      </c>
-      <c r="B63">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>224</v>
-      </c>
-      <c r="B64">
-        <v>4424341.028821101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>249</v>
-      </c>
-      <c r="B65">
-        <v>4186169.152985218</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>225</v>
-      </c>
-      <c r="B66">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>226</v>
-      </c>
-      <c r="B67">
-        <v>4651279.543866448</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>250</v>
-      </c>
-      <c r="B68">
-        <v>4189368.912780208</v>
+        <v>3961335.593607123</v>
       </c>
     </row>
   </sheetData>
@@ -6905,37 +5572,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>273</v>
+      <c r="A1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="B2">
         <v>17.65832997587177</v>
       </c>
       <c r="C2">
-        <v>17.6583299758716</v>
+        <v>17.65832997585875</v>
       </c>
       <c r="D2">
         <v>65.15454188318284</v>
@@ -6944,21 +5611,21 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520399999989</v>
+        <v>1150.520399999152</v>
       </c>
       <c r="G2">
-        <v>-9.657213157497654E-13</v>
+        <v>-7.371672710223209E-11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="B3">
         <v>45.91165732334162</v>
       </c>
       <c r="C3">
-        <v>45.91165732334163</v>
+        <v>45.91165732334165</v>
       </c>
       <c r="D3">
         <v>65.15454188318284</v>
@@ -6967,21 +5634,21 @@
         <v>2991.353</v>
       </c>
       <c r="F3">
-        <v>2991.353000000001</v>
+        <v>2991.353000000002</v>
       </c>
       <c r="G3">
-        <v>1.547630334396267E-14</v>
+        <v>6.190521337585069E-14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="B4">
         <v>35.31665995174353</v>
       </c>
       <c r="C4">
-        <v>35.31665995174353</v>
+        <v>35.31665995174356</v>
       </c>
       <c r="D4">
         <v>65.15454188318284</v>
@@ -6990,10 +5657,843 @@
         <v>2301.0408</v>
       </c>
       <c r="F4">
-        <v>2301.0408</v>
+        <v>2301.040800000002</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>8.047677631248045E-14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H7" t="s">
+        <v>268</v>
+      </c>
+      <c r="I7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G8" t="s">
+        <v>275</v>
+      </c>
+      <c r="H8" t="s">
+        <v>276</v>
+      </c>
+      <c r="I8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" t="s">
+        <v>268</v>
+      </c>
+      <c r="G9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H9" t="s">
+        <v>280</v>
+      </c>
+      <c r="I9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>283</v>
+      </c>
+      <c r="B11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>285</v>
+      </c>
+      <c r="B13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" t="s">
+        <v>265</v>
+      </c>
+      <c r="D13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E13" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" t="s">
+        <v>276</v>
+      </c>
+      <c r="G14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C16" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" t="s">
+        <v>276</v>
+      </c>
+      <c r="E16" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B17" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>293</v>
+      </c>
+      <c r="B20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" t="s">
+        <v>294</v>
+      </c>
+      <c r="E20" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G20" t="s">
+        <v>297</v>
+      </c>
+      <c r="H20" t="s">
+        <v>298</v>
+      </c>
+      <c r="I20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>299</v>
+      </c>
+      <c r="B21" t="s">
+        <v>279</v>
+      </c>
+      <c r="C21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D21" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" t="s">
+        <v>300</v>
+      </c>
+      <c r="F21" t="s">
+        <v>296</v>
+      </c>
+      <c r="G21" t="s">
+        <v>297</v>
+      </c>
+      <c r="H21" t="s">
+        <v>298</v>
+      </c>
+      <c r="I21" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>301</v>
+      </c>
+      <c r="B22" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>303</v>
+      </c>
+      <c r="B23" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>305</v>
+      </c>
+      <c r="B24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>306</v>
+      </c>
+      <c r="B25" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>308</v>
+      </c>
+      <c r="B26" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>309</v>
+      </c>
+      <c r="B27" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>310</v>
+      </c>
+      <c r="B28" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B31" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>319</v>
+      </c>
+      <c r="B33" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>320</v>
+      </c>
+      <c r="B34" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>321</v>
+      </c>
+      <c r="B35" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>323</v>
+      </c>
+      <c r="B36" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>325</v>
+      </c>
+      <c r="B37" t="s">
+        <v>326</v>
+      </c>
+      <c r="C37" t="s">
+        <v>256</v>
+      </c>
+      <c r="D37" t="s">
+        <v>327</v>
+      </c>
+      <c r="E37" t="s">
+        <v>295</v>
+      </c>
+      <c r="F37" t="s">
+        <v>328</v>
+      </c>
+      <c r="G37" t="s">
+        <v>260</v>
+      </c>
+      <c r="H37" t="s">
+        <v>329</v>
+      </c>
+      <c r="I37" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C38" t="s">
+        <v>332</v>
+      </c>
+      <c r="D38" t="s">
+        <v>327</v>
+      </c>
+      <c r="E38" t="s">
+        <v>295</v>
+      </c>
+      <c r="F38" t="s">
+        <v>328</v>
+      </c>
+      <c r="G38" t="s">
+        <v>260</v>
+      </c>
+      <c r="H38" t="s">
+        <v>329</v>
+      </c>
+      <c r="I38" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>333</v>
+      </c>
+      <c r="B39" t="s">
+        <v>326</v>
+      </c>
+      <c r="C39" t="s">
+        <v>334</v>
+      </c>
+      <c r="D39" t="s">
+        <v>327</v>
+      </c>
+      <c r="E39" t="s">
+        <v>295</v>
+      </c>
+      <c r="F39" t="s">
+        <v>328</v>
+      </c>
+      <c r="G39" t="s">
+        <v>260</v>
+      </c>
+      <c r="H39" t="s">
+        <v>329</v>
+      </c>
+      <c r="I39" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>335</v>
+      </c>
+      <c r="B40" t="s">
+        <v>326</v>
+      </c>
+      <c r="C40" t="s">
+        <v>256</v>
+      </c>
+      <c r="D40" t="s">
+        <v>327</v>
+      </c>
+      <c r="E40" t="s">
+        <v>295</v>
+      </c>
+      <c r="F40" t="s">
+        <v>328</v>
+      </c>
+      <c r="G40" t="s">
+        <v>260</v>
+      </c>
+      <c r="H40" t="s">
+        <v>329</v>
+      </c>
+      <c r="I40" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>336</v>
+      </c>
+      <c r="B41" t="s">
+        <v>326</v>
+      </c>
+      <c r="C41" t="s">
+        <v>337</v>
+      </c>
+      <c r="D41" t="s">
+        <v>327</v>
+      </c>
+      <c r="E41" t="s">
+        <v>295</v>
+      </c>
+      <c r="F41" t="s">
+        <v>328</v>
+      </c>
+      <c r="G41" t="s">
+        <v>260</v>
+      </c>
+      <c r="H41" t="s">
+        <v>329</v>
+      </c>
+      <c r="I41" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>338</v>
+      </c>
+      <c r="B42" t="s">
+        <v>326</v>
+      </c>
+      <c r="C42" t="s">
+        <v>339</v>
+      </c>
+      <c r="D42" t="s">
+        <v>327</v>
+      </c>
+      <c r="E42" t="s">
+        <v>295</v>
+      </c>
+      <c r="F42" t="s">
+        <v>328</v>
+      </c>
+      <c r="G42" t="s">
+        <v>260</v>
+      </c>
+      <c r="H42" t="s">
+        <v>329</v>
+      </c>
+      <c r="I42" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>340</v>
+      </c>
+      <c r="B43" t="s">
+        <v>326</v>
+      </c>
+      <c r="C43" t="s">
+        <v>265</v>
+      </c>
+      <c r="D43" t="s">
+        <v>327</v>
+      </c>
+      <c r="E43" t="s">
+        <v>295</v>
+      </c>
+      <c r="F43" t="s">
+        <v>328</v>
+      </c>
+      <c r="G43" t="s">
+        <v>260</v>
+      </c>
+      <c r="H43" t="s">
+        <v>329</v>
+      </c>
+      <c r="I43" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>326</v>
+      </c>
+      <c r="C44" t="s">
+        <v>256</v>
+      </c>
+      <c r="D44" t="s">
+        <v>327</v>
+      </c>
+      <c r="E44" t="s">
+        <v>295</v>
+      </c>
+      <c r="F44" t="s">
+        <v>328</v>
+      </c>
+      <c r="G44" t="s">
+        <v>260</v>
+      </c>
+      <c r="H44" t="s">
+        <v>329</v>
+      </c>
+      <c r="I44" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>341</v>
+      </c>
+      <c r="B45" t="s">
+        <v>326</v>
+      </c>
+      <c r="C45" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45" t="s">
+        <v>327</v>
+      </c>
+      <c r="E45" t="s">
+        <v>295</v>
+      </c>
+      <c r="F45" t="s">
+        <v>328</v>
+      </c>
+      <c r="G45" t="s">
+        <v>260</v>
+      </c>
+      <c r="H45" t="s">
+        <v>329</v>
+      </c>
+      <c r="I45" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>342</v>
+      </c>
+      <c r="B46" t="s">
+        <v>326</v>
+      </c>
+      <c r="C46" t="s">
+        <v>343</v>
+      </c>
+      <c r="D46" t="s">
+        <v>344</v>
+      </c>
+      <c r="E46" t="s">
+        <v>345</v>
+      </c>
+      <c r="F46" t="s">
+        <v>276</v>
+      </c>
+      <c r="G46" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>346</v>
+      </c>
+      <c r="B47" t="s">
+        <v>326</v>
+      </c>
+      <c r="C47" t="s">
+        <v>314</v>
+      </c>
+      <c r="D47" t="s">
+        <v>344</v>
+      </c>
+      <c r="E47" t="s">
+        <v>265</v>
+      </c>
+      <c r="F47" t="s">
+        <v>276</v>
+      </c>
+      <c r="G47" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>347</v>
+      </c>
+      <c r="B48" t="s">
+        <v>326</v>
+      </c>
+      <c r="C48" t="s">
+        <v>314</v>
+      </c>
+      <c r="D48" t="s">
+        <v>344</v>
+      </c>
+      <c r="E48" t="s">
+        <v>265</v>
+      </c>
+      <c r="F48" t="s">
+        <v>276</v>
+      </c>
+      <c r="G48" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>348</v>
+      </c>
+      <c r="B49" t="s">
+        <v>326</v>
+      </c>
+      <c r="C49" t="s">
+        <v>343</v>
+      </c>
+      <c r="D49" t="s">
+        <v>344</v>
+      </c>
+      <c r="E49" t="s">
+        <v>265</v>
+      </c>
+      <c r="F49" t="s">
+        <v>276</v>
+      </c>
+      <c r="G49" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>349</v>
+      </c>
+      <c r="B50" t="s">
+        <v>326</v>
+      </c>
+      <c r="C50" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" t="s">
+        <v>276</v>
+      </c>
+      <c r="E50" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
